--- a/annotation_categories/catalan/dataset_CAT_csv_categories.xlsx
+++ b/annotation_categories/catalan/dataset_CAT_csv_categories.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\TFM\b_Dataset\Dataset\Final_Datasets_tobesent\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC818CC-FD42-45B6-8E95-01BF98D5E814}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA18785A-78CD-4063-BC95-AAD39FA5B006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="190" windowWidth="19200" windowHeight="11090" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="2" r:id="rId1"/>
@@ -5294,9 +5294,6 @@
     <t>4.1</t>
   </si>
   <si>
-    <t>macrocategory</t>
-  </si>
-  <si>
     <t>subcategory</t>
   </si>
   <si>
@@ -9717,6 +9714,9 @@
   </si>
   <si>
     <t>Hyperbole and exaggeration</t>
+  </si>
+  <si>
+    <t>category</t>
   </si>
 </sst>
 </file>
@@ -10240,11 +10240,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -13287,13 +13287,13 @@
         <v>360</v>
       </c>
       <c r="C1" s="28" t="s">
-        <v>718</v>
+        <v>924</v>
       </c>
       <c r="D1" s="28" t="s">
         <v>708</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="F1" s="28" t="s">
         <v>172</v>
@@ -13354,16 +13354,16 @@
         <v>281</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C2" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D2" s="49" t="s">
         <v>711</v>
       </c>
       <c r="E2" s="49" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F2" s="25" t="s">
         <v>510</v>
@@ -13422,16 +13422,16 @@
         <v>281</v>
       </c>
       <c r="B3" s="24" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D3" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E3" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F3" s="25" t="s">
         <v>514</v>
@@ -13489,16 +13489,16 @@
         <v>281</v>
       </c>
       <c r="B4" s="24" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="C4" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D4" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F4" s="25" t="s">
         <v>525</v>
@@ -13556,16 +13556,16 @@
         <v>281</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C5" s="50" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D5" s="51" t="s">
         <v>717</v>
       </c>
       <c r="E5" s="51" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F5" s="25" t="s">
         <v>530</v>
@@ -13623,16 +13623,16 @@
         <v>281</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C6" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D6" s="23" t="s">
         <v>716</v>
       </c>
       <c r="E6" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F6" s="25" t="s">
         <v>534</v>
@@ -13690,16 +13690,16 @@
         <v>281</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D7" s="51" t="s">
         <v>717</v>
       </c>
       <c r="E7" s="51" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F7" s="25" t="s">
         <v>536</v>
@@ -13757,16 +13757,16 @@
         <v>281</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C8" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>709</v>
       </c>
       <c r="E8" s="23" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F8" s="25" t="s">
         <v>537</v>
@@ -13827,13 +13827,13 @@
         <v>678</v>
       </c>
       <c r="C9" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>168</v>
       </c>
       <c r="E9" s="23" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F9" s="25" t="s">
         <v>499</v>
@@ -13892,16 +13892,16 @@
         <v>281</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D10" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E10" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F10" s="25" t="s">
         <v>551</v>
@@ -13960,16 +13960,16 @@
         <v>281</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C11" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D11" s="23" t="s">
         <v>715</v>
       </c>
       <c r="E11" s="23" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F11" s="25" t="s">
         <v>555</v>
@@ -14029,16 +14029,16 @@
         <v>281</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C12" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D12" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F12" s="25" t="s">
         <v>556</v>
@@ -14096,16 +14096,16 @@
         <v>281</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C13" s="50" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D13" s="51" t="s">
         <v>717</v>
       </c>
       <c r="E13" s="51" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F13" s="25" t="s">
         <v>558</v>
@@ -14166,13 +14166,13 @@
         <v>683</v>
       </c>
       <c r="C14" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D14" s="23" t="s">
         <v>714</v>
       </c>
       <c r="E14" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F14" s="25" t="s">
         <v>559</v>
@@ -14230,16 +14230,16 @@
         <v>281</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="C15" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D15" s="23" t="s">
         <v>714</v>
       </c>
       <c r="E15" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F15" s="25" t="s">
         <v>560</v>
@@ -14297,16 +14297,16 @@
         <v>281</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C16" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D16" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E16" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F16" s="25" t="s">
         <v>563</v>
@@ -14367,13 +14367,13 @@
         <v>684</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D17" s="23" t="s">
         <v>716</v>
       </c>
       <c r="E17" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F17" s="25" t="s">
         <v>570</v>
@@ -14431,16 +14431,16 @@
         <v>281</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="C18" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D18" s="23" t="s">
         <v>714</v>
       </c>
       <c r="E18" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F18" s="25" t="s">
         <v>579</v>
@@ -14499,16 +14499,16 @@
         <v>281</v>
       </c>
       <c r="B19" s="25" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C19" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D19" s="23" t="s">
         <v>169</v>
       </c>
       <c r="E19" s="23" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F19" s="25" t="s">
         <v>581</v>
@@ -14569,16 +14569,16 @@
         <v>281</v>
       </c>
       <c r="B20" s="25" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C20" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D20" s="23" t="s">
         <v>716</v>
       </c>
       <c r="E20" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F20" s="25" t="s">
         <v>583</v>
@@ -14636,16 +14636,16 @@
         <v>281</v>
       </c>
       <c r="B21" s="25" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="C21" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D21" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E21" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F21" s="25" t="s">
         <v>597</v>
@@ -14703,16 +14703,16 @@
         <v>281</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="C22" s="45" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D22" s="46" t="s">
         <v>710</v>
       </c>
       <c r="E22" s="47" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F22" s="25" t="s">
         <v>598</v>
@@ -14770,16 +14770,16 @@
         <v>281</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="C23" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D23" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E23" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F23" s="25" t="s">
         <v>600</v>
@@ -14840,16 +14840,16 @@
         <v>281</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="C24" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D24" s="23" t="s">
         <v>714</v>
       </c>
       <c r="E24" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F24" s="25" t="s">
         <v>602</v>
@@ -14910,16 +14910,16 @@
         <v>281</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C25" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D25" s="23" t="s">
         <v>715</v>
       </c>
       <c r="E25" s="23" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F25" s="25" t="s">
         <v>605</v>
@@ -14978,16 +14978,16 @@
         <v>281</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C26" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D26" s="23" t="s">
         <v>715</v>
       </c>
       <c r="E26" s="23" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F26" s="25" t="s">
         <v>606</v>
@@ -15046,16 +15046,16 @@
         <v>281</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C27" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D27" s="49" t="s">
         <v>713</v>
       </c>
       <c r="E27" s="49" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F27" s="25" t="s">
         <v>609</v>
@@ -15113,16 +15113,16 @@
         <v>281</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="C28" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D28" s="49" t="s">
         <v>711</v>
       </c>
       <c r="E28" s="49" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F28" s="24" t="s">
         <v>499</v>
@@ -15180,16 +15180,16 @@
         <v>281</v>
       </c>
       <c r="B29" s="24" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D29" s="51" t="s">
         <v>717</v>
       </c>
       <c r="E29" s="51" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F29" s="24" t="s">
         <v>620</v>
@@ -15247,16 +15247,16 @@
         <v>281</v>
       </c>
       <c r="B30" s="24" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="C30" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D30" s="23" t="s">
         <v>715</v>
       </c>
       <c r="E30" s="23" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F30" s="24" t="s">
         <v>623</v>
@@ -15316,16 +15316,16 @@
         <v>281</v>
       </c>
       <c r="B31" s="24" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C31" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D31" s="23" t="s">
         <v>714</v>
       </c>
       <c r="E31" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F31" s="24" t="s">
         <v>499</v>
@@ -15383,16 +15383,16 @@
         <v>281</v>
       </c>
       <c r="B32" s="24" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C32" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D32" s="23" t="s">
         <v>715</v>
       </c>
       <c r="E32" s="23" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F32" s="24" t="s">
         <v>626</v>
@@ -15451,19 +15451,19 @@
         <v>281</v>
       </c>
       <c r="B33" s="24" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C33" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D33" s="23" t="s">
         <v>716</v>
       </c>
       <c r="E33" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F33" s="24" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="H33" s="20"/>
       <c r="K33" s="63"/>
@@ -15519,16 +15519,16 @@
         <v>281</v>
       </c>
       <c r="B34" s="24" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C34" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D34" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E34" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F34" s="24" t="s">
         <v>631</v>
@@ -15588,16 +15588,16 @@
         <v>281</v>
       </c>
       <c r="B35" s="24" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C35" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D35" s="49" t="s">
         <v>713</v>
       </c>
       <c r="E35" s="49" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F35" s="24" t="s">
         <v>635</v>
@@ -15656,16 +15656,16 @@
         <v>281</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C36" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D36" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E36" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F36" s="24" t="s">
         <v>640</v>
@@ -15724,16 +15724,16 @@
         <v>281</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C37" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D37" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E37" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F37" s="24" t="s">
         <v>641</v>
@@ -15792,16 +15792,16 @@
         <v>281</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="C38" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D38" s="23" t="s">
         <v>714</v>
       </c>
       <c r="E38" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F38" s="24" t="s">
         <v>643</v>
@@ -15863,13 +15863,13 @@
         <v>701</v>
       </c>
       <c r="C39" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D39" s="23" t="s">
         <v>714</v>
       </c>
       <c r="E39" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F39" s="24" t="s">
         <v>645</v>
@@ -15927,16 +15927,16 @@
         <v>281</v>
       </c>
       <c r="B40" s="24" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C40" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D40" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E40" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F40" s="24" t="s">
         <v>499</v>
@@ -15994,16 +15994,16 @@
         <v>281</v>
       </c>
       <c r="B41" s="24" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C41" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D41" s="23" t="s">
         <v>716</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F41" s="24" t="s">
         <v>647</v>
@@ -16062,16 +16062,16 @@
         <v>281</v>
       </c>
       <c r="B42" s="24" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C42" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D42" s="49" t="s">
         <v>713</v>
       </c>
       <c r="E42" s="49" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F42" s="24" t="s">
         <v>648</v>
@@ -16129,16 +16129,16 @@
         <v>281</v>
       </c>
       <c r="B43" s="24" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="C43" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D43" s="23" t="s">
         <v>714</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F43" s="24" t="s">
         <v>652</v>
@@ -16196,16 +16196,16 @@
         <v>281</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C44" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D44" s="23" t="s">
         <v>714</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F44" s="24" t="s">
         <v>653</v>
@@ -16263,16 +16263,16 @@
         <v>281</v>
       </c>
       <c r="B45" s="24" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C45" s="50" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D45" s="51" t="s">
         <v>717</v>
       </c>
       <c r="E45" s="51" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F45" s="24" t="s">
         <v>655</v>
@@ -16330,16 +16330,16 @@
         <v>281</v>
       </c>
       <c r="B46" s="24" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="C46" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D46" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F46" s="24" t="s">
         <v>668</v>
@@ -16400,13 +16400,13 @@
         <v>707</v>
       </c>
       <c r="C47" s="45" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D47" s="46" t="s">
         <v>710</v>
       </c>
       <c r="E47" s="47" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F47" s="24" t="s">
         <v>669</v>
@@ -16464,16 +16464,16 @@
         <v>388</v>
       </c>
       <c r="B48" s="24" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C48" s="50" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D48" s="51" t="s">
         <v>717</v>
       </c>
       <c r="E48" s="51" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F48" s="25" t="s">
         <v>529</v>
@@ -16535,16 +16535,16 @@
         <v>685</v>
       </c>
       <c r="C49" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D49" s="23" t="s">
         <v>716</v>
       </c>
       <c r="E49" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F49" s="25" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="G49" s="57"/>
       <c r="H49" s="13"/>
@@ -16605,13 +16605,13 @@
         <v>671</v>
       </c>
       <c r="C50" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D50" s="23" t="s">
         <v>709</v>
       </c>
       <c r="E50" s="23" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F50" s="25" t="s">
         <v>499</v>
@@ -16672,16 +16672,16 @@
         <v>422</v>
       </c>
       <c r="B51" s="25" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C51" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D51" s="49" t="s">
         <v>713</v>
       </c>
       <c r="E51" s="49" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F51" s="25" t="s">
         <v>573</v>
@@ -16743,13 +16743,13 @@
         <v>698</v>
       </c>
       <c r="C52" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D52" s="49" t="s">
         <v>713</v>
       </c>
       <c r="E52" s="49" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F52" s="24" t="s">
         <v>499</v>
@@ -16812,19 +16812,19 @@
         <v>483</v>
       </c>
       <c r="C53" s="45" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D53" s="46" t="s">
         <v>710</v>
       </c>
       <c r="E53" s="47" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F53" s="24" t="s">
         <v>650</v>
       </c>
       <c r="H53" s="20"/>
-      <c r="K53" s="65"/>
+      <c r="K53" s="64"/>
       <c r="L53" s="32"/>
       <c r="M53" s="20"/>
       <c r="N53" s="19"/>
@@ -16877,22 +16877,22 @@
         <v>390</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C54" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D54" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E54" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F54" s="25" t="s">
         <v>533</v>
       </c>
       <c r="H54" s="20"/>
-      <c r="K54" s="65"/>
+      <c r="K54" s="64"/>
       <c r="L54" s="32"/>
       <c r="M54" s="20"/>
       <c r="N54" s="19"/>
@@ -16945,16 +16945,16 @@
         <v>437</v>
       </c>
       <c r="B55" s="25" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C55" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D55" s="23" t="s">
         <v>169</v>
       </c>
       <c r="E55" s="23" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F55" s="24" t="s">
         <v>591</v>
@@ -17013,16 +17013,16 @@
         <v>475</v>
       </c>
       <c r="B56" s="24" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C56" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D56" s="23" t="s">
         <v>169</v>
       </c>
       <c r="E56" s="23" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F56" s="24" t="s">
         <v>638</v>
@@ -17081,16 +17081,16 @@
         <v>431</v>
       </c>
       <c r="B57" s="25" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C57" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D57" s="23" t="s">
         <v>715</v>
       </c>
       <c r="E57" s="23" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F57" s="25" t="s">
         <v>584</v>
@@ -17148,16 +17148,16 @@
         <v>401</v>
       </c>
       <c r="B58" s="24" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="C58" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D58" s="23" t="s">
         <v>714</v>
       </c>
       <c r="E58" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F58" s="25" t="s">
         <v>545</v>
@@ -17215,16 +17215,16 @@
         <v>374</v>
       </c>
       <c r="B59" s="24" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C59" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D59" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E59" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F59" s="25" t="s">
         <v>515</v>
@@ -17283,16 +17283,16 @@
         <v>444</v>
       </c>
       <c r="B60" s="25" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C60" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D60" s="23" t="s">
         <v>715</v>
       </c>
       <c r="E60" s="23" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F60" s="25" t="s">
         <v>595</v>
@@ -17350,16 +17350,16 @@
         <v>419</v>
       </c>
       <c r="B61" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C61" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D61" s="23" t="s">
         <v>714</v>
       </c>
       <c r="E61" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F61" s="25" t="s">
         <v>569</v>
@@ -17417,16 +17417,16 @@
         <v>449</v>
       </c>
       <c r="B62" s="25" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C62" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D62" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E62" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F62" s="25" t="s">
         <v>604</v>
@@ -17485,16 +17485,16 @@
         <v>399</v>
       </c>
       <c r="B63" s="24" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C63" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D63" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E63" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F63" s="25" t="s">
         <v>543</v>
@@ -17552,16 +17552,16 @@
         <v>494</v>
       </c>
       <c r="B64" s="24" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="C64" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D64" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E64" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F64" s="24" t="s">
         <v>664</v>
@@ -17619,16 +17619,16 @@
         <v>463</v>
       </c>
       <c r="B65" s="24" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C65" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D65" s="23" t="s">
         <v>716</v>
       </c>
       <c r="E65" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F65" s="24" t="s">
         <v>625</v>
@@ -17686,16 +17686,16 @@
         <v>367</v>
       </c>
       <c r="B66" s="24" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C66" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D66" s="23" t="s">
         <v>714</v>
       </c>
       <c r="E66" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F66" s="25" t="s">
         <v>505</v>
@@ -17753,19 +17753,19 @@
         <v>451</v>
       </c>
       <c r="B67" s="25" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C67" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D67" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E67" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F67" s="25" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="H67" s="20"/>
       <c r="L67" s="19"/>
@@ -17820,16 +17820,16 @@
         <v>436</v>
       </c>
       <c r="B68" s="25" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C68" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D68" s="23" t="s">
         <v>168</v>
       </c>
       <c r="E68" s="23" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F68" s="24" t="s">
         <v>590</v>
@@ -17888,16 +17888,16 @@
         <v>471</v>
       </c>
       <c r="B69" s="24" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="C69" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D69" s="23" t="s">
         <v>714</v>
       </c>
       <c r="E69" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F69" s="24" t="s">
         <v>636</v>
@@ -17959,16 +17959,16 @@
         <v>689</v>
       </c>
       <c r="C70" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D70" s="49" t="s">
         <v>713</v>
       </c>
       <c r="E70" s="49" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F70" s="25" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="H70" s="20"/>
       <c r="L70" s="19"/>
@@ -18023,16 +18023,16 @@
         <v>404</v>
       </c>
       <c r="B71" s="25" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C71" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D71" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E71" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F71" s="25" t="s">
         <v>548</v>
@@ -18094,13 +18094,13 @@
         <v>686</v>
       </c>
       <c r="C72" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D72" s="49" t="s">
         <v>711</v>
       </c>
       <c r="E72" s="49" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F72" s="25" t="s">
         <v>499</v>
@@ -18161,19 +18161,19 @@
         <v>461</v>
       </c>
       <c r="B73" s="24" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="C73" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D73" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E73" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F73" s="24" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="H73" s="20"/>
       <c r="L73" s="19"/>
@@ -18228,16 +18228,16 @@
         <v>439</v>
       </c>
       <c r="B74" s="25" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C74" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D74" s="23" t="s">
         <v>709</v>
       </c>
       <c r="E74" s="23" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F74" s="25" t="s">
         <v>440</v>
@@ -18297,16 +18297,16 @@
         <v>492</v>
       </c>
       <c r="B75" s="24" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C75" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D75" s="23" t="s">
         <v>169</v>
       </c>
       <c r="E75" s="23" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F75" s="24" t="s">
         <v>662</v>
@@ -18365,16 +18365,16 @@
         <v>481</v>
       </c>
       <c r="B76" s="24" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C76" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D76" s="23" t="s">
         <v>715</v>
       </c>
       <c r="E76" s="23" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F76" s="24" t="s">
         <v>649</v>
@@ -18432,16 +18432,16 @@
         <v>424</v>
       </c>
       <c r="B77" s="25" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="C77" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D77" s="23" t="s">
         <v>168</v>
       </c>
       <c r="E77" s="23" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F77" s="25" t="s">
         <v>575</v>
@@ -18500,16 +18500,16 @@
         <v>371</v>
       </c>
       <c r="B78" s="24" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C78" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D78" s="23" t="s">
         <v>716</v>
       </c>
       <c r="E78" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F78" s="25" t="s">
         <v>509</v>
@@ -18565,19 +18565,19 @@
     </row>
     <row r="79" spans="1:57" ht="76" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="24" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B79" s="24" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="C79" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D79" s="49" t="s">
         <v>171</v>
       </c>
       <c r="E79" s="49" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F79" s="24" t="s">
         <v>617</v>
@@ -18635,16 +18635,16 @@
         <v>472</v>
       </c>
       <c r="B80" s="24" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C80" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D80" s="23" t="s">
         <v>714</v>
       </c>
       <c r="E80" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F80" s="24" t="s">
         <v>637</v>
@@ -18700,19 +18700,19 @@
     </row>
     <row r="81" spans="1:57" ht="76" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="25" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="B81" s="25" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C81" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D81" s="23" t="s">
         <v>716</v>
       </c>
       <c r="E81" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F81" s="25" t="s">
         <v>611</v>
@@ -18770,16 +18770,16 @@
         <v>376</v>
       </c>
       <c r="B82" s="24" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C82" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D82" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E82" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F82" s="25" t="s">
         <v>517</v>
@@ -18840,13 +18840,13 @@
         <v>699</v>
       </c>
       <c r="C83" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D83" s="23" t="s">
         <v>716</v>
       </c>
       <c r="E83" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F83" s="24" t="s">
         <v>499</v>
@@ -18907,13 +18907,13 @@
         <v>682</v>
       </c>
       <c r="C84" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D84" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E84" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F84" s="25" t="s">
         <v>411</v>
@@ -18971,16 +18971,16 @@
         <v>423</v>
       </c>
       <c r="B85" s="25" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C85" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D85" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E85" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F85" s="25" t="s">
         <v>574</v>
@@ -19041,13 +19041,13 @@
         <v>704</v>
       </c>
       <c r="C86" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D86" s="23" t="s">
         <v>709</v>
       </c>
       <c r="E86" s="23" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F86" s="24" t="s">
         <v>660</v>
@@ -19108,16 +19108,16 @@
         <v>370</v>
       </c>
       <c r="B87" s="24" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C87" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D87" s="23" t="s">
         <v>715</v>
       </c>
       <c r="E87" s="23" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F87" s="25" t="s">
         <v>508</v>
@@ -19178,16 +19178,16 @@
         <v>385</v>
       </c>
       <c r="B88" s="24" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C88" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D88" s="23" t="s">
         <v>716</v>
       </c>
       <c r="E88" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F88" s="25" t="s">
         <v>526</v>
@@ -19249,16 +19249,16 @@
         <v>389</v>
       </c>
       <c r="B89" s="24" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C89" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D89" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E89" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F89" s="25" t="s">
         <v>532</v>
@@ -19319,16 +19319,16 @@
         <v>368</v>
       </c>
       <c r="B90" s="24" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C90" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D90" s="49" t="s">
         <v>711</v>
       </c>
       <c r="E90" s="49" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F90" s="25" t="s">
         <v>506</v>
@@ -19387,19 +19387,19 @@
     </row>
     <row r="91" spans="1:57" ht="76" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="24" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="B91" s="24" t="s">
         <v>702</v>
       </c>
       <c r="C91" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D91" s="23" t="s">
         <v>716</v>
       </c>
       <c r="E91" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F91" s="24" t="s">
         <v>646</v>
@@ -19460,16 +19460,16 @@
         <v>408</v>
       </c>
       <c r="B92" s="25" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C92" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D92" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E92" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F92" s="25" t="s">
         <v>553</v>
@@ -19533,13 +19533,13 @@
         <v>688</v>
       </c>
       <c r="C93" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D93" s="49" t="s">
         <v>171</v>
       </c>
       <c r="E93" s="49" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F93" s="25" t="s">
         <v>586</v>
@@ -19600,16 +19600,16 @@
         <v>363</v>
       </c>
       <c r="B94" s="24" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C94" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D94" s="49" t="s">
         <v>711</v>
       </c>
       <c r="E94" s="49" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F94" s="25" t="s">
         <v>501</v>
@@ -19667,19 +19667,19 @@
     </row>
     <row r="95" spans="1:57" ht="76" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="24" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B95" s="24" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="C95" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D95" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E95" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F95" s="24" t="s">
         <v>624</v>
@@ -19738,16 +19738,16 @@
         <v>377</v>
       </c>
       <c r="B96" s="24" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C96" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D96" s="49" t="s">
         <v>713</v>
       </c>
       <c r="E96" s="49" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F96" s="25" t="s">
         <v>518</v>
@@ -19806,16 +19806,16 @@
         <v>434</v>
       </c>
       <c r="B97" s="25" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C97" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D97" s="49" t="s">
         <v>711</v>
       </c>
       <c r="E97" s="49" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F97" s="25" t="s">
         <v>588</v>
@@ -19874,16 +19874,16 @@
         <v>445</v>
       </c>
       <c r="B98" s="25" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C98" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D98" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E98" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F98" s="25" t="s">
         <v>596</v>
@@ -19942,16 +19942,16 @@
         <v>464</v>
       </c>
       <c r="B99" s="24" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="C99" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D99" s="23" t="s">
         <v>715</v>
       </c>
       <c r="E99" s="23" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F99" s="24" t="s">
         <v>627</v>
@@ -20011,16 +20011,16 @@
         <v>362</v>
       </c>
       <c r="B100" s="24" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C100" s="45" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D100" s="46" t="s">
         <v>710</v>
       </c>
       <c r="E100" s="47" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F100" s="25" t="s">
         <v>500</v>
@@ -20080,16 +20080,16 @@
         <v>484</v>
       </c>
       <c r="B101" s="24" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C101" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D101" s="23" t="s">
         <v>168</v>
       </c>
       <c r="E101" s="23" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F101" s="24" t="s">
         <v>651</v>
@@ -20149,16 +20149,16 @@
         <v>496</v>
       </c>
       <c r="B102" s="24" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="C102" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D102" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E102" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F102" s="24" t="s">
         <v>666</v>
@@ -20218,16 +20218,16 @@
         <v>458</v>
       </c>
       <c r="B103" s="24" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="C103" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D103" s="23" t="s">
         <v>714</v>
       </c>
       <c r="E103" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F103" s="24" t="s">
         <v>616</v>
@@ -20283,19 +20283,19 @@
     </row>
     <row r="104" spans="1:57" ht="76" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="25" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="B104" s="24" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C104" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D104" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E104" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F104" s="25" t="s">
         <v>531</v>
@@ -20350,19 +20350,19 @@
     </row>
     <row r="105" spans="1:57" ht="76" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="25" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B105" s="25" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C105" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D105" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E105" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F105" s="25" t="s">
         <v>577</v>
@@ -20421,16 +20421,16 @@
         <v>381</v>
       </c>
       <c r="B106" s="24" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="C106" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D106" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E106" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F106" s="25" t="s">
         <v>521</v>
@@ -20489,16 +20489,16 @@
         <v>420</v>
       </c>
       <c r="B107" s="25" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C107" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D107" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E107" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F107" s="25" t="s">
         <v>571</v>
@@ -20557,16 +20557,16 @@
         <v>405</v>
       </c>
       <c r="B108" s="25" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C108" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D108" s="23" t="s">
         <v>168</v>
       </c>
       <c r="E108" s="23" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F108" s="25" t="s">
         <v>549</v>
@@ -20627,13 +20627,13 @@
         <v>672</v>
       </c>
       <c r="C109" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D109" s="23" t="s">
         <v>709</v>
       </c>
       <c r="E109" s="23" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F109" s="25" t="s">
         <v>507</v>
@@ -20691,16 +20691,16 @@
         <v>428</v>
       </c>
       <c r="B110" s="25" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C110" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D110" s="23" t="s">
         <v>715</v>
       </c>
       <c r="E110" s="23" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F110" s="25" t="s">
         <v>578</v>
@@ -20761,13 +20761,13 @@
         <v>697</v>
       </c>
       <c r="C111" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D111" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E111" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F111" s="24" t="s">
         <v>633</v>
@@ -20825,16 +20825,16 @@
         <v>421</v>
       </c>
       <c r="B112" s="25" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C112" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D112" s="49" t="s">
         <v>713</v>
       </c>
       <c r="E112" s="49" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F112" s="25" t="s">
         <v>572</v>
@@ -20895,13 +20895,13 @@
         <v>705</v>
       </c>
       <c r="C113" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D113" s="23" t="s">
         <v>709</v>
       </c>
       <c r="E113" s="23" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F113" s="24" t="s">
         <v>661</v>
@@ -20959,16 +20959,16 @@
         <v>462</v>
       </c>
       <c r="B114" s="24" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C114" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D114" s="23" t="s">
         <v>169</v>
       </c>
       <c r="E114" s="23" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F114" s="24" t="s">
         <v>622</v>
@@ -21026,16 +21026,16 @@
         <v>440</v>
       </c>
       <c r="B115" s="25" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C115" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D115" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E115" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F115" s="25" t="s">
         <v>593</v>
@@ -21093,16 +21093,16 @@
         <v>435</v>
       </c>
       <c r="B116" s="25" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C116" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D116" s="23" t="s">
         <v>714</v>
       </c>
       <c r="E116" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F116" s="25" t="s">
         <v>589</v>
@@ -21160,16 +21160,16 @@
         <v>457</v>
       </c>
       <c r="B117" s="24" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="C117" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D117" s="49" t="s">
         <v>713</v>
       </c>
       <c r="E117" s="49" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F117" s="24" t="s">
         <v>615</v>
@@ -21230,13 +21230,13 @@
         <v>687</v>
       </c>
       <c r="C118" s="45" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D118" s="46" t="s">
         <v>710</v>
       </c>
       <c r="E118" s="47" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F118" s="25" t="s">
         <v>585</v>
@@ -21294,16 +21294,16 @@
         <v>415</v>
       </c>
       <c r="B119" s="25" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C119" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D119" s="23" t="s">
         <v>716</v>
       </c>
       <c r="E119" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F119" s="25" t="s">
         <v>565</v>
@@ -21362,16 +21362,16 @@
         <v>395</v>
       </c>
       <c r="B120" s="24" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C120" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D120" s="23" t="s">
         <v>716</v>
       </c>
       <c r="E120" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F120" s="25" t="s">
         <v>540</v>
@@ -21430,16 +21430,16 @@
         <v>425</v>
       </c>
       <c r="B121" s="25" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C121" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D121" s="23" t="s">
         <v>709</v>
       </c>
       <c r="E121" s="23" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F121" s="25" t="s">
         <v>576</v>
@@ -21497,19 +21497,19 @@
         <v>384</v>
       </c>
       <c r="B122" s="24" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C122" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D122" s="23" t="s">
         <v>169</v>
       </c>
       <c r="E122" s="23" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F122" s="25" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="H122" s="20"/>
       <c r="L122" s="19"/>
@@ -21564,16 +21564,16 @@
         <v>438</v>
       </c>
       <c r="B123" s="25" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C123" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D123" s="23" t="s">
         <v>714</v>
       </c>
       <c r="E123" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F123" s="25" t="s">
         <v>592</v>
@@ -21632,16 +21632,16 @@
         <v>447</v>
       </c>
       <c r="B124" s="25" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C124" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D124" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E124" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F124" s="25" t="s">
         <v>599</v>
@@ -21702,13 +21702,13 @@
         <v>681</v>
       </c>
       <c r="C125" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D125" s="23" t="s">
         <v>715</v>
       </c>
       <c r="E125" s="23" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F125" s="25" t="s">
         <v>544</v>
@@ -21766,16 +21766,16 @@
         <v>413</v>
       </c>
       <c r="B126" s="25" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C126" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D126" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E126" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F126" s="25" t="s">
         <v>562</v>
@@ -21833,16 +21833,16 @@
         <v>495</v>
       </c>
       <c r="B127" s="24" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="C127" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D127" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E127" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F127" s="24" t="s">
         <v>665</v>
@@ -21897,19 +21897,19 @@
     </row>
     <row r="128" spans="1:57" ht="76" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="25" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B128" s="25" t="s">
         <v>692</v>
       </c>
       <c r="C128" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D128" s="49" t="s">
         <v>713</v>
       </c>
       <c r="E128" s="49" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F128" s="25" t="s">
         <v>613</v>
@@ -21965,19 +21965,19 @@
     </row>
     <row r="129" spans="1:57" ht="76" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="25" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B129" s="25" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C129" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D129" s="23" t="s">
         <v>709</v>
       </c>
       <c r="E129" s="23" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F129" s="25" t="s">
         <v>587</v>
@@ -22035,16 +22035,16 @@
         <v>455</v>
       </c>
       <c r="B130" s="24" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C130" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D130" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E130" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F130" s="24" t="s">
         <v>612</v>
@@ -22102,16 +22102,16 @@
         <v>429</v>
       </c>
       <c r="B131" s="25" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C131" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D131" s="23" t="s">
         <v>169</v>
       </c>
       <c r="E131" s="23" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F131" s="25" t="s">
         <v>580</v>
@@ -22169,16 +22169,16 @@
         <v>470</v>
       </c>
       <c r="B132" s="24" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C132" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D132" s="23" t="s">
         <v>715</v>
       </c>
       <c r="E132" s="23" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F132" s="24" t="s">
         <v>634</v>
@@ -22236,16 +22236,16 @@
         <v>383</v>
       </c>
       <c r="B133" s="24" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C133" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D133" s="23" t="s">
         <v>709</v>
       </c>
       <c r="E133" s="23" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F133" s="25" t="s">
         <v>523</v>
@@ -22303,16 +22303,16 @@
         <v>364</v>
       </c>
       <c r="B134" s="24" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C134" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D134" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E134" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F134" s="25" t="s">
         <v>502</v>
@@ -22367,19 +22367,19 @@
     </row>
     <row r="135" spans="1:57" ht="76" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="25" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="B135" s="25" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C135" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D135" s="23" t="s">
         <v>169</v>
       </c>
       <c r="E135" s="23" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F135" s="25" t="s">
         <v>603</v>
@@ -22437,16 +22437,16 @@
         <v>441</v>
       </c>
       <c r="B136" s="25" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C136" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D136" s="23" t="s">
         <v>168</v>
       </c>
       <c r="E136" s="23" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F136" s="25" t="s">
         <v>594</v>
@@ -22503,19 +22503,19 @@
     </row>
     <row r="137" spans="1:57" ht="76" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="24" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B137" s="26" t="s">
         <v>676</v>
       </c>
       <c r="C137" s="45" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D137" s="46" t="s">
         <v>710</v>
       </c>
       <c r="E137" s="47" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F137" s="24" t="s">
         <v>499</v>
@@ -22576,16 +22576,16 @@
         <v>488</v>
       </c>
       <c r="B138" s="24" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C138" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D138" s="23" t="s">
         <v>714</v>
       </c>
       <c r="E138" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F138" s="24" t="s">
         <v>658</v>
@@ -22646,16 +22646,16 @@
         <v>418</v>
       </c>
       <c r="B139" s="25" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C139" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D139" s="23" t="s">
         <v>709</v>
       </c>
       <c r="E139" s="23" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F139" s="25" t="s">
         <v>568</v>
@@ -22717,13 +22717,13 @@
         <v>700</v>
       </c>
       <c r="C140" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D140" s="23" t="s">
         <v>168</v>
       </c>
       <c r="E140" s="23" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F140" s="24" t="s">
         <v>499</v>
@@ -22782,19 +22782,19 @@
         <v>450</v>
       </c>
       <c r="B141" s="25" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C141" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D141" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E141" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F141" s="25" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="H141" s="20"/>
       <c r="K141" s="58"/>
@@ -22850,16 +22850,16 @@
         <v>402</v>
       </c>
       <c r="B142" s="24" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C142" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D142" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E142" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F142" s="25" t="s">
         <v>546</v>
@@ -22918,16 +22918,16 @@
         <v>465</v>
       </c>
       <c r="B143" s="24" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C143" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D143" s="23" t="s">
         <v>716</v>
       </c>
       <c r="E143" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F143" s="24" t="s">
         <v>628</v>
@@ -22989,13 +22989,13 @@
         <v>695</v>
       </c>
       <c r="C144" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D144" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E144" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F144" s="24" t="s">
         <v>499</v>
@@ -23053,16 +23053,16 @@
         <v>386</v>
       </c>
       <c r="B145" s="24" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C145" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D145" s="23" t="s">
         <v>715</v>
       </c>
       <c r="E145" s="23" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F145" s="25" t="s">
         <v>527</v>
@@ -23124,13 +23124,13 @@
         <v>673</v>
       </c>
       <c r="C146" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D146" s="23" t="s">
         <v>709</v>
       </c>
       <c r="E146" s="23" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F146" s="25" t="s">
         <v>519</v>
@@ -23186,19 +23186,19 @@
     </row>
     <row r="147" spans="1:57" ht="76" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A147" s="25" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B147" s="24" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C147" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D147" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E147" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F147" s="25" t="s">
         <v>512</v>
@@ -23257,16 +23257,16 @@
         <v>498</v>
       </c>
       <c r="B148" s="24" t="s">
+        <v>906</v>
+      </c>
+      <c r="C148" s="44" t="s">
         <v>907</v>
-      </c>
-      <c r="C148" s="44" t="s">
-        <v>908</v>
       </c>
       <c r="D148" s="23" t="s">
         <v>716</v>
       </c>
       <c r="E148" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F148" s="24" t="s">
         <v>670</v>
@@ -23325,16 +23325,16 @@
         <v>493</v>
       </c>
       <c r="B149" s="24" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C149" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D149" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E149" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F149" s="24" t="s">
         <v>663</v>
@@ -23394,16 +23394,16 @@
         <v>407</v>
       </c>
       <c r="B150" s="25" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C150" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D150" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E150" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F150" s="25" t="s">
         <v>552</v>
@@ -23460,19 +23460,19 @@
     </row>
     <row r="151" spans="1:57" ht="76" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A151" s="24" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B151" s="24" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C151" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D151" s="23" t="s">
         <v>716</v>
       </c>
       <c r="E151" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F151" s="24" t="s">
         <v>516</v>
@@ -23532,16 +23532,16 @@
         <v>487</v>
       </c>
       <c r="B152" s="24" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C152" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D152" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E152" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F152" s="24" t="s">
         <v>657</v>
@@ -23600,16 +23600,16 @@
         <v>454</v>
       </c>
       <c r="B153" s="25" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="C153" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D153" s="49" t="s">
         <v>713</v>
       </c>
       <c r="E153" s="49" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F153" s="25" t="s">
         <v>610</v>
@@ -23668,16 +23668,16 @@
         <v>417</v>
       </c>
       <c r="B154" s="25" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C154" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D154" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E154" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F154" s="25" t="s">
         <v>567</v>
@@ -23733,19 +23733,19 @@
     </row>
     <row r="155" spans="1:57" ht="76" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="24" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="B155" s="24" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C155" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D155" s="23" t="s">
         <v>709</v>
       </c>
       <c r="E155" s="23" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F155" s="24" t="s">
         <v>536</v>
@@ -23804,16 +23804,16 @@
         <v>373</v>
       </c>
       <c r="B156" s="24" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C156" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D156" s="23" t="s">
         <v>709</v>
       </c>
       <c r="E156" s="23" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F156" s="25" t="s">
         <v>513</v>
@@ -23871,16 +23871,16 @@
         <v>398</v>
       </c>
       <c r="B157" s="24" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C157" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D157" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E157" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F157" s="25" t="s">
         <v>399</v>
@@ -23938,16 +23938,16 @@
         <v>372</v>
       </c>
       <c r="B158" s="24" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C158" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D158" s="23" t="s">
         <v>169</v>
       </c>
       <c r="E158" s="23" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F158" s="25" t="s">
         <v>511</v>
@@ -24002,22 +24002,22 @@
     </row>
     <row r="159" spans="1:57" ht="76" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A159" s="25" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B159" s="27" t="s">
         <v>690</v>
       </c>
       <c r="C159" s="45" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="D159" s="46" t="s">
         <v>710</v>
       </c>
       <c r="E159" s="47" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="F159" s="25" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="H159" s="20"/>
       <c r="K159" s="19"/>
@@ -24073,16 +24073,16 @@
         <v>406</v>
       </c>
       <c r="B160" s="25" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="C160" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D160" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E160" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F160" s="25" t="s">
         <v>550</v>
@@ -24141,22 +24141,22 @@
         <v>397</v>
       </c>
       <c r="B161" s="24" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C161" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D161" s="23" t="s">
         <v>168</v>
       </c>
       <c r="E161" s="23" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F161" s="25" t="s">
         <v>542</v>
       </c>
       <c r="H161" s="20"/>
-      <c r="K161" s="64"/>
+      <c r="K161" s="65"/>
       <c r="L161" s="19"/>
       <c r="M161" s="20"/>
       <c r="N161" s="19"/>
@@ -24209,23 +24209,23 @@
         <v>403</v>
       </c>
       <c r="B162" s="25" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C162" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D162" s="23" t="s">
         <v>714</v>
       </c>
       <c r="E162" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F162" s="25" t="s">
         <v>547</v>
       </c>
       <c r="G162" s="20"/>
       <c r="H162" s="20"/>
-      <c r="K162" s="64"/>
+      <c r="K162" s="65"/>
       <c r="L162" s="19"/>
       <c r="M162" s="20"/>
       <c r="N162" s="19"/>
@@ -24281,13 +24281,13 @@
         <v>674</v>
       </c>
       <c r="C163" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D163" s="23" t="s">
         <v>716</v>
       </c>
       <c r="E163" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F163" s="25" t="s">
         <v>520</v>
@@ -24346,16 +24346,16 @@
         <v>460</v>
       </c>
       <c r="B164" s="24" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="C164" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D164" s="49" t="s">
         <v>711</v>
       </c>
       <c r="E164" s="49" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F164" s="24" t="s">
         <v>619</v>
@@ -24411,22 +24411,22 @@
     </row>
     <row r="165" spans="1:57" ht="76" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A165" s="24" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B165" s="24" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C165" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D165" s="49" t="s">
         <v>711</v>
       </c>
       <c r="E165" s="49" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F165" s="24" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="G165" s="13"/>
       <c r="H165" s="13"/>
@@ -24486,13 +24486,13 @@
         <v>703</v>
       </c>
       <c r="C166" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D166" s="23" t="s">
         <v>716</v>
       </c>
       <c r="E166" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F166" s="24" t="s">
         <v>654</v>
@@ -24551,16 +24551,16 @@
         <v>448</v>
       </c>
       <c r="B167" s="25" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="C167" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D167" s="23" t="s">
         <v>714</v>
       </c>
       <c r="E167" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F167" s="25" t="s">
         <v>601</v>
@@ -24619,16 +24619,16 @@
         <v>365</v>
       </c>
       <c r="B168" s="24" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C168" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D168" s="49" t="s">
         <v>713</v>
       </c>
       <c r="E168" s="49" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F168" s="25" t="s">
         <v>503</v>
@@ -24686,16 +24686,16 @@
         <v>382</v>
       </c>
       <c r="B169" s="24" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C169" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D169" s="23" t="s">
         <v>716</v>
       </c>
       <c r="E169" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F169" s="25" t="s">
         <v>522</v>
@@ -24758,13 +24758,13 @@
         <v>706</v>
       </c>
       <c r="C170" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D170" s="23" t="s">
         <v>716</v>
       </c>
       <c r="E170" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F170" s="24" t="s">
         <v>667</v>
@@ -24826,13 +24826,13 @@
         <v>696</v>
       </c>
       <c r="C171" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D171" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E171" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F171" s="24" t="s">
         <v>632</v>
@@ -24892,16 +24892,16 @@
         <v>430</v>
       </c>
       <c r="B172" s="25" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="C172" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D172" s="23" t="s">
         <v>714</v>
       </c>
       <c r="E172" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F172" s="25" t="s">
         <v>582</v>
@@ -24959,16 +24959,16 @@
         <v>414</v>
       </c>
       <c r="B173" s="24" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C173" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D173" s="23" t="s">
         <v>169</v>
       </c>
       <c r="E173" s="23" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F173" s="24" t="s">
         <v>564</v>
@@ -25026,16 +25026,16 @@
         <v>380</v>
       </c>
       <c r="B174" s="24" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C174" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D174" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E174" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F174" s="25" t="s">
         <v>499</v>
@@ -25093,16 +25093,16 @@
         <v>366</v>
       </c>
       <c r="B175" s="24" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="C175" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D175" s="23" t="s">
         <v>709</v>
       </c>
       <c r="E175" s="23" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F175" s="25" t="s">
         <v>504</v>
@@ -25162,13 +25162,13 @@
         <v>677</v>
       </c>
       <c r="C176" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D176" s="49" t="s">
         <v>713</v>
       </c>
       <c r="E176" s="49" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F176" s="25" t="s">
         <v>536</v>
@@ -25227,19 +25227,19 @@
         <v>375</v>
       </c>
       <c r="B177" s="24" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C177" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D177" s="23" t="s">
         <v>168</v>
       </c>
       <c r="E177" s="23" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F177" s="25" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="H177" s="20"/>
       <c r="K177" s="63"/>
@@ -25295,16 +25295,16 @@
         <v>459</v>
       </c>
       <c r="B178" s="24" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C178" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D178" s="49" t="s">
         <v>171</v>
       </c>
       <c r="E178" s="49" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F178" s="24" t="s">
         <v>618</v>
@@ -25365,13 +25365,13 @@
         <v>477</v>
       </c>
       <c r="C179" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D179" s="49" t="s">
         <v>171</v>
       </c>
       <c r="E179" s="49" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F179" s="24" t="s">
         <v>639</v>
@@ -25430,16 +25430,16 @@
         <v>480</v>
       </c>
       <c r="B180" s="24" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="C180" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D180" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E180" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F180" s="24" t="s">
         <v>644</v>
@@ -25501,13 +25501,13 @@
         <v>680</v>
       </c>
       <c r="C181" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D181" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E181" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F181" s="25" t="s">
         <v>541</v>
@@ -25566,16 +25566,16 @@
         <v>486</v>
       </c>
       <c r="B182" s="24" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C182" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D182" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E182" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F182" s="24" t="s">
         <v>656</v>
@@ -25634,16 +25634,16 @@
         <v>456</v>
       </c>
       <c r="B183" s="24" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C183" s="50" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D183" s="51" t="s">
         <v>717</v>
       </c>
       <c r="E183" s="51" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F183" s="24" t="s">
         <v>614</v>
@@ -25703,16 +25703,16 @@
         <v>443</v>
       </c>
       <c r="B184" s="25" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C184" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D184" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E184" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F184" s="25" t="s">
         <v>499</v>
@@ -25769,19 +25769,19 @@
     </row>
     <row r="185" spans="1:57" ht="76" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A185" s="25" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B185" s="24" t="s">
         <v>675</v>
       </c>
       <c r="C185" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D185" s="23" t="s">
         <v>716</v>
       </c>
       <c r="E185" s="23" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F185" s="25" t="s">
         <v>524</v>
@@ -25837,19 +25837,19 @@
     </row>
     <row r="186" spans="1:57" ht="76" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A186" s="24" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B186" s="24" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C186" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D186" s="23" t="s">
         <v>169</v>
       </c>
       <c r="E186" s="23" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F186" s="24" t="s">
         <v>621</v>
@@ -25908,16 +25908,16 @@
         <v>411</v>
       </c>
       <c r="B187" s="25" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="C187" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D187" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E187" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F187" s="25" t="s">
         <v>557</v>
@@ -25978,13 +25978,13 @@
         <v>691</v>
       </c>
       <c r="C188" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D188" s="23" t="s">
         <v>173</v>
       </c>
       <c r="E188" s="23" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="F188" s="25" t="s">
         <v>608</v>
@@ -26042,16 +26042,16 @@
         <v>391</v>
       </c>
       <c r="B189" s="24" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C189" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D189" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E189" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F189" s="25" t="s">
         <v>535</v>
@@ -26112,13 +26112,13 @@
         <v>694</v>
       </c>
       <c r="C190" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D190" s="23" t="s">
         <v>715</v>
       </c>
       <c r="E190" s="23" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F190" s="24" t="s">
         <v>630</v>
@@ -26176,16 +26176,16 @@
         <v>387</v>
       </c>
       <c r="B191" s="24" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C191" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D191" s="23" t="s">
         <v>715</v>
       </c>
       <c r="E191" s="23" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F191" s="24" t="s">
         <v>528</v>
@@ -26243,16 +26243,16 @@
         <v>409</v>
       </c>
       <c r="B192" s="25" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C192" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D192" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E192" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F192" s="25" t="s">
         <v>554</v>
@@ -26310,16 +26310,16 @@
         <v>489</v>
       </c>
       <c r="B193" s="24" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C193" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D193" s="49" t="s">
         <v>171</v>
       </c>
       <c r="E193" s="49" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F193" s="24" t="s">
         <v>659</v>
@@ -26377,16 +26377,16 @@
         <v>412</v>
       </c>
       <c r="B194" s="25" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C194" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D194" s="49" t="s">
         <v>713</v>
       </c>
       <c r="E194" s="49" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F194" s="25" t="s">
         <v>561</v>
@@ -26447,13 +26447,13 @@
         <v>679</v>
       </c>
       <c r="C195" s="48" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D195" s="49" t="s">
         <v>713</v>
       </c>
       <c r="E195" s="49" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F195" s="25" t="s">
         <v>538</v>
@@ -26514,16 +26514,16 @@
         <v>416</v>
       </c>
       <c r="B196" s="25" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C196" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D196" s="23" t="s">
         <v>168</v>
       </c>
       <c r="E196" s="23" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F196" s="25" t="s">
         <v>566</v>
@@ -26583,16 +26583,16 @@
         <v>446</v>
       </c>
       <c r="B197" s="25" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="C197" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D197" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E197" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F197" s="25" t="s">
         <v>499</v>
@@ -26652,16 +26652,16 @@
         <v>452</v>
       </c>
       <c r="B198" s="24" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C198" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D198" s="23" t="s">
         <v>714</v>
       </c>
       <c r="E198" s="23" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F198" s="25" t="s">
         <v>607</v>
@@ -26718,19 +26718,19 @@
     </row>
     <row r="199" spans="1:57" ht="76" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A199" s="24" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B199" s="24" t="s">
         <v>693</v>
       </c>
       <c r="C199" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D199" s="23" t="s">
         <v>169</v>
       </c>
       <c r="E199" s="23" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="F199" s="24" t="s">
         <v>629</v>
@@ -26789,16 +26789,16 @@
         <v>394</v>
       </c>
       <c r="B200" s="24" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C200" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D200" s="23" t="s">
         <v>712</v>
       </c>
       <c r="E200" s="23" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F200" s="25" t="s">
         <v>539</v>
@@ -26857,16 +26857,16 @@
         <v>479</v>
       </c>
       <c r="B201" s="24" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C201" s="44" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D201" s="23" t="s">
         <v>168</v>
       </c>
       <c r="E201" s="23" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F201" s="24" t="s">
         <v>642</v>
@@ -29636,6 +29636,13 @@
     </sortState>
   </autoFilter>
   <mergeCells count="15">
+    <mergeCell ref="J248:J249"/>
+    <mergeCell ref="K248:K249"/>
+    <mergeCell ref="K55:K56"/>
+    <mergeCell ref="K105:K107"/>
+    <mergeCell ref="K145:K146"/>
+    <mergeCell ref="K147:K148"/>
+    <mergeCell ref="K161:K162"/>
     <mergeCell ref="K9:K10"/>
     <mergeCell ref="K18:K19"/>
     <mergeCell ref="K176:K177"/>
@@ -29644,13 +29651,6 @@
     <mergeCell ref="K25:K26"/>
     <mergeCell ref="K32:K34"/>
     <mergeCell ref="K53:K54"/>
-    <mergeCell ref="J248:J249"/>
-    <mergeCell ref="K248:K249"/>
-    <mergeCell ref="K55:K56"/>
-    <mergeCell ref="K105:K107"/>
-    <mergeCell ref="K145:K146"/>
-    <mergeCell ref="K147:K148"/>
-    <mergeCell ref="K161:K162"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
